--- a/ds/planejamento/1semestre/planos/Planos_de_Ensino_LER.xlsx
+++ b/ds/planejamento/1semestre/planos/Planos_de_Ensino_LER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\senai2026\ds\planejamento\1semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C33F939-D1E4-49CF-A613-2599303E1600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0364BB-3448-492A-8A0A-BD10C356DBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano de Ensino1" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="117">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -342,19 +342,10 @@
     <t>Projeto, Empresa modelo, proposta de solução de problema. Apresentação de resultados através de eminário.</t>
   </si>
   <si>
-    <t>Você e seus amigos decidiram montar uma startup de desenvolvimento de software com o objetivo de desenvolver soluções e sistemas aproveitando as infraestruturas de nuvem que as gigantes (Big techs [Apple, Microsoft, Google, Amazon e Meta)]) do mercado oferecem.</t>
-  </si>
-  <si>
     <t>4 Aplicar processos Design Thinking para abordar processos complexos e desenvolver soluções inovadoras</t>
   </si>
   <si>
     <t>Pequisou soluções, tirou dúvidas com os colegas e instrutores e apresentou a solução</t>
-  </si>
-  <si>
-    <t>Pesquisou e documentou as regras de negócio e requisitos funcionais e não funcionais</t>
-  </si>
-  <si>
-    <t>Criou o documento de requisitos ilustrando os requisitos funcionais com diagramas de casos de uso</t>
   </si>
   <si>
     <t>Cada integrante do grupo desempenhou um papel no desenvolvimento da solução e ou protótipo.</t>
@@ -565,12 +556,6 @@
     </r>
   </si>
   <si>
-    <t>Acertou todos os critérios críticos e pelo menos 2 dos 3 desejáveis</t>
-  </si>
-  <si>
-    <t>Acertou todos os critérios críticos e pelo menos 1 dos 3 desejáveis</t>
-  </si>
-  <si>
     <t>Carga Horária Presencial: 40</t>
   </si>
   <si>
@@ -593,6 +578,50 @@
 Utilize diagramas de casos de uso para ilustrar os requisitos funcionais e diagramas de rede, mapas mentais ou fluxogramas para ilustrar os requisitos não funcionais. Desenvolva um ou mais protótipos funcionais da solução utilizando Canvas ou Figma - Escolha uma metodologia ágil, justifique a escolha e distribua os papéis e responsabilidades pelo seu grupo
 [Capacidade:  5 Aplicar ferramentas de metodologias ágeis na gestão de projetos e desenvolvimento de produtos]
 [Capacidade: 4 Demonstrar autonomia]</t>
+  </si>
+  <si>
+    <t>Em um ambiente empreendedor, seus colegas de turma e você decidiram montar uma startup de desenvolvimento de software com o objetivo de desenvolver soluções e sistemas aproveitando as infraestruturas de nuvem que as gigantes (Big techs [Apple, Microsoft, Google, Amazon e Meta)]) do mercado oferecem.</t>
+  </si>
+  <si>
+    <t>Documentou equisitos funcionais e não funcionais</t>
+  </si>
+  <si>
+    <t>Elencou as regras de negócio</t>
+  </si>
+  <si>
+    <t>Criou o documento de requisitos</t>
+  </si>
+  <si>
+    <t>Ilustrou os requisitos funcionais com diagramas de casos de uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Registrar requisitos funcionais e não funcionais, de acordo com as informações coletadas com o cliente.
+1. Demonstrar autogestão 
+2. Demonstrar pensamento analítico 	
+3. Demonstrar inteligência emocional	
+4 Demonstrar autonomia	</t>
+  </si>
+  <si>
+    <t>Compreende como os elementos do sistema se relacionam</t>
+  </si>
+  <si>
+    <t>Como a solução é aplicada para resolver o problema proposto</t>
+  </si>
+  <si>
+    <t>Pequisou soluções, tirou dúvidas com os colegas e instrutores</t>
+  </si>
+  <si>
+    <t>Apresentou a solução</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 5 dos 6 desejáveis</t>
+  </si>
+  <si>
+    <t>3 Identificar práticas ágeis de acordo com as características e requisitos do projeto
+1. Demonstrar autogestão 
+2. Demonstrar pensamento analítico 	
+3. Demonstrar inteligência emocional	
+4 Demonstrar autonomia</t>
   </si>
 </sst>
 </file>
@@ -872,7 +901,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1242,11 +1271,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1347,47 +1424,169 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1424,141 +1623,43 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1569,36 +1670,6 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1612,7 +1683,16 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1621,14 +1701,41 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1934,7 +2041,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA942"/>
+  <dimension ref="A1:AA949"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -1951,134 +2058,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="40" t="s">
+      <c r="B2" s="118"/>
+      <c r="C2" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="45" t="s">
+      <c r="D2" s="111"/>
+      <c r="E2" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="39" t="s">
+      <c r="F2" s="115"/>
+      <c r="G2" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="95"/>
+      <c r="I2" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="39"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="47" t="s">
+      <c r="A3" s="117"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="50" t="s">
+      <c r="F3" s="116"/>
+      <c r="G3" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="50"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="98"/>
+      <c r="C4" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="61" t="s">
-        <v>106</v>
+      <c r="D4" s="94"/>
+      <c r="E4" s="105" t="s">
+        <v>101</v>
       </c>
-      <c r="F4" s="62"/>
-      <c r="G4" s="50" t="s">
+      <c r="F4" s="106"/>
+      <c r="G4" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="63" t="s">
+      <c r="A5" s="98"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="56" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="136" t="s">
-        <v>107</v>
+      <c r="D6" s="100"/>
+      <c r="E6" s="83" t="s">
+        <v>102</v>
       </c>
-      <c r="F6" s="66"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
     </row>
     <row r="7" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="101"/>
     </row>
     <row r="9" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
@@ -2099,14 +2206,14 @@
       <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58" t="s">
+      <c r="H9" s="102"/>
+      <c r="I9" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="102"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2141,17 +2248,17 @@
       <c r="E10" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="59" t="s">
+      <c r="H10" s="104"/>
+      <c r="I10" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="J10" s="60"/>
+      <c r="J10" s="104"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2186,17 +2293,15 @@
       <c r="E11" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="59" t="s">
+      <c r="F11" s="139"/>
+      <c r="G11" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="60"/>
-      <c r="I11" s="51" t="s">
+      <c r="H11" s="104"/>
+      <c r="I11" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="52"/>
+      <c r="J11" s="96"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -2217,13 +2322,13 @@
     </row>
     <row r="12" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2">
         <v>12</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>72</v>
@@ -2231,17 +2336,15 @@
       <c r="E12" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="51" t="s">
+      <c r="F12" s="140"/>
+      <c r="G12" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="135"/>
-      <c r="I12" s="51" t="s">
+      <c r="H12" s="39"/>
+      <c r="I12" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="135"/>
+      <c r="J12" s="39"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2272,10 +2375,10 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="122"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2295,18 +2398,18 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="125"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="47"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2326,18 +2429,18 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="126" t="s">
+      <c r="A15" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2357,18 +2460,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="104" t="s">
-        <v>87</v>
+      <c r="A16" s="44" t="s">
+        <v>105</v>
       </c>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2388,18 +2491,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2419,18 +2522,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="233.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="104" t="s">
-        <v>103</v>
+      <c r="A18" s="44" t="s">
+        <v>100</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
@@ -2446,18 +2549,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="126" t="s">
+      <c r="A19" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2477,18 +2580,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="104" t="s">
-        <v>96</v>
+      <c r="A20" s="44" t="s">
+        <v>93</v>
       </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2508,18 +2611,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="105"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2539,22 +2642,22 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="101" t="s">
+      <c r="A22" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="103" t="s">
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="106" t="s">
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2574,12 +2677,12 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="102"/>
-      <c r="B23" s="102"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
       <c r="G23" s="21">
         <v>1</v>
       </c>
@@ -2610,24 +2713,24 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="67" t="s">
+    <row r="24" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="70"/>
-      <c r="D24" s="71" t="s">
-        <v>90</v>
+      <c r="C24" s="126"/>
+      <c r="D24" s="80" t="s">
+        <v>107</v>
       </c>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
       <c r="G24" s="7"/>
       <c r="H24" s="18"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="1"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2645,21 +2748,19 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="68"/>
-      <c r="B25" s="69" t="s">
-        <v>73</v>
+    <row r="25" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="137"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="80" t="s">
+        <v>106</v>
       </c>
-      <c r="C25" s="70"/>
-      <c r="D25" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
       <c r="G25" s="7"/>
       <c r="H25" s="18"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2678,23 +2779,21 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="87" t="s">
-        <v>27</v>
+    <row r="26" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="137"/>
+      <c r="B26" s="125" t="s">
+        <v>73</v>
       </c>
-      <c r="B26" s="84" t="s">
-        <v>38</v>
+      <c r="C26" s="126"/>
+      <c r="D26" s="80" t="s">
+        <v>108</v>
       </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="71" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="74"/>
-      <c r="F26" s="75"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77"/>
       <c r="G26" s="7"/>
       <c r="H26" s="18"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -2713,17 +2812,15 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="88"/>
-      <c r="B27" s="84" t="s">
-        <v>43</v>
+    <row r="27" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="146"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="129" t="s">
+        <v>109</v>
       </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="86" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="77"/>
       <c r="G27" s="7"/>
       <c r="H27" s="18"/>
       <c r="I27" s="14"/>
@@ -2746,17 +2843,19 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="88"/>
-      <c r="B28" s="84" t="s">
-        <v>39</v>
+    <row r="28" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="78" t="s">
+        <v>27</v>
       </c>
-      <c r="C28" s="85"/>
-      <c r="D28" s="86" t="s">
-        <v>95</v>
+      <c r="B28" s="73" t="s">
+        <v>38</v>
       </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="81"/>
+      <c r="F28" s="82"/>
       <c r="G28" s="7"/>
       <c r="H28" s="18"/>
       <c r="I28" s="14"/>
@@ -2779,17 +2878,17 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="88"/>
-      <c r="B29" s="84" t="s">
-        <v>60</v>
+    <row r="29" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="78"/>
+      <c r="B29" s="141" t="s">
+        <v>43</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="86" t="s">
-        <v>89</v>
+      <c r="C29" s="142"/>
+      <c r="D29" s="75" t="s">
+        <v>111</v>
       </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="77"/>
       <c r="G29" s="7"/>
       <c r="H29" s="18"/>
       <c r="I29" s="14"/>
@@ -2812,17 +2911,19 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="83"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+    <row r="30" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="79"/>
+      <c r="B30" s="143"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="75" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="76"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2841,21 +2942,21 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="79" t="s">
-        <v>12</v>
+    <row r="31" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="79"/>
+      <c r="B31" s="73" t="s">
+        <v>39</v>
       </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82" t="s">
-        <v>13</v>
+      <c r="C31" s="74"/>
+      <c r="D31" s="75" t="s">
+        <v>92</v>
       </c>
-      <c r="G31" s="80"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -2874,23 +2975,21 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <v>6</v>
+    <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="79"/>
+      <c r="B32" s="141" t="s">
+        <v>60</v>
       </c>
-      <c r="B32" s="93" t="s">
-        <v>14</v>
+      <c r="C32" s="142"/>
+      <c r="D32" s="75" t="s">
+        <v>113</v>
       </c>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="92">
-        <v>100</v>
-      </c>
-      <c r="G32" s="90"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -2909,23 +3008,19 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
-        <v>4</v>
+    <row r="33" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="79"/>
+      <c r="B33" s="143"/>
+      <c r="C33" s="128"/>
+      <c r="D33" s="75" t="s">
+        <v>114</v>
       </c>
-      <c r="B33" s="94" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="95"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="97">
-        <v>80</v>
-      </c>
-      <c r="G33" s="98"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2945,20 +3040,14 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
-        <v>3</v>
-      </c>
-      <c r="B34" s="100" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92">
-        <v>60</v>
-      </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2979,21 +3068,19 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
-        <v>2</v>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35" s="68" t="s">
+        <v>12</v>
       </c>
-      <c r="B35" s="89" t="s">
-        <v>15</v>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71" t="s">
+        <v>13</v>
       </c>
-      <c r="C35" s="90"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="92">
-        <v>50</v>
-      </c>
-      <c r="G35" s="90"/>
-      <c r="H35" s="91"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="70"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -3014,21 +3101,21 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
-      <c r="B36" s="93" t="s">
-        <v>16</v>
+      <c r="B36" s="50" t="s">
+        <v>14</v>
       </c>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="92">
-        <v>30</v>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="53">
+        <v>100</v>
       </c>
-      <c r="G36" s="90"/>
-      <c r="H36" s="91"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -3049,15 +3136,21 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
+    <row r="37" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>7</v>
+      </c>
+      <c r="B37" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="62"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="64">
+        <v>95</v>
+      </c>
+      <c r="G37" s="65"/>
+      <c r="H37" s="66"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -3078,21 +3171,21 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="16" t="s">
-        <v>17</v>
+    <row r="38" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>6</v>
       </c>
-      <c r="E38" s="16" t="s">
-        <v>18</v>
+      <c r="B38" s="61" t="s">
+        <v>57</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>19</v>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="64">
+        <v>90</v>
       </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="66"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -3113,25 +3206,21 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="17" t="s">
-        <v>20</v>
+    <row r="39" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>5</v>
       </c>
-      <c r="E39" s="109">
-        <v>1</v>
+      <c r="B39" s="61" t="s">
+        <v>54</v>
       </c>
-      <c r="F39" s="109">
-        <v>0</v>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="64">
+        <v>80</v>
       </c>
-      <c r="G39" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="H39" s="112" t="s">
-        <v>53</v>
-      </c>
+      <c r="G39" s="65"/>
+      <c r="H39" s="66"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -3152,17 +3241,21 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="27" t="s">
-        <v>21</v>
+    <row r="40" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>4</v>
       </c>
-      <c r="E40" s="110"/>
-      <c r="F40" s="110"/>
-      <c r="G40" s="111"/>
-      <c r="H40" s="113"/>
+      <c r="B40" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="64">
+        <v>70</v>
+      </c>
+      <c r="G40" s="65"/>
+      <c r="H40" s="66"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -3183,19 +3276,23 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="108" t="s">
-        <v>36</v>
+    <row r="41" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>3</v>
       </c>
-      <c r="B41" s="108"/>
-      <c r="C41" s="108"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="108"/>
-      <c r="F41" s="108"/>
-      <c r="G41" s="108"/>
-      <c r="H41" s="108"/>
-      <c r="I41" s="108"/>
-      <c r="J41" s="108"/>
+      <c r="B41" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="53">
+        <v>60</v>
+      </c>
+      <c r="G41" s="51"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -3214,15 +3311,21 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="4"/>
+    <row r="42" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>2</v>
+      </c>
+      <c r="B42" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="53">
+        <v>50</v>
+      </c>
+      <c r="G42" s="51"/>
+      <c r="H42" s="52"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3243,15 +3346,21 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="4"/>
+    <row r="43" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>1</v>
+      </c>
+      <c r="B43" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53">
+        <v>30</v>
+      </c>
+      <c r="G43" s="51"/>
+      <c r="H43" s="52"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3273,14 +3382,14 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="4"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3301,15 +3410,21 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="4"/>
+    <row r="45" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -3330,15 +3445,25 @@
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
     </row>
-    <row r="46" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="4"/>
+    <row r="46" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="54">
+        <v>1</v>
+      </c>
+      <c r="F46" s="54">
+        <v>0</v>
+      </c>
+      <c r="G46" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="H46" s="58" t="s">
+        <v>53</v>
+      </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3359,15 +3484,17 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
     </row>
-    <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="4"/>
+    <row r="47" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="144"/>
+      <c r="H47" s="59"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3388,17 +3515,19 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
     </row>
-    <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+    <row r="48" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -6897,208 +7026,208 @@
       <c r="Z168" s="1"/>
       <c r="AA168" s="1"/>
     </row>
-    <row r="169" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
-      <c r="L169" s="6"/>
-      <c r="M169" s="6"/>
-      <c r="N169" s="6"/>
-      <c r="O169" s="6"/>
-      <c r="P169" s="6"/>
-      <c r="Q169" s="6"/>
-      <c r="R169" s="6"/>
-      <c r="S169" s="6"/>
-      <c r="T169" s="6"/>
-      <c r="U169" s="6"/>
-      <c r="V169" s="6"/>
-      <c r="W169" s="6"/>
-      <c r="X169" s="6"/>
-      <c r="Y169" s="6"/>
-      <c r="Z169" s="6"/>
-      <c r="AA169" s="6"/>
-    </row>
-    <row r="170" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
-      <c r="L170" s="6"/>
-      <c r="M170" s="6"/>
-      <c r="N170" s="6"/>
-      <c r="O170" s="6"/>
-      <c r="P170" s="6"/>
-      <c r="Q170" s="6"/>
-      <c r="R170" s="6"/>
-      <c r="S170" s="6"/>
-      <c r="T170" s="6"/>
-      <c r="U170" s="6"/>
-      <c r="V170" s="6"/>
-      <c r="W170" s="6"/>
-      <c r="X170" s="6"/>
-      <c r="Y170" s="6"/>
-      <c r="Z170" s="6"/>
-      <c r="AA170" s="6"/>
-    </row>
-    <row r="171" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
-      <c r="M171" s="6"/>
-      <c r="N171" s="6"/>
-      <c r="O171" s="6"/>
-      <c r="P171" s="6"/>
-      <c r="Q171" s="6"/>
-      <c r="R171" s="6"/>
-      <c r="S171" s="6"/>
-      <c r="T171" s="6"/>
-      <c r="U171" s="6"/>
-      <c r="V171" s="6"/>
-      <c r="W171" s="6"/>
-      <c r="X171" s="6"/>
-      <c r="Y171" s="6"/>
-      <c r="Z171" s="6"/>
-      <c r="AA171" s="6"/>
-    </row>
-    <row r="172" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
-      <c r="L172" s="6"/>
-      <c r="M172" s="6"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="6"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="6"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="6"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="6"/>
-    </row>
-    <row r="173" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
-      <c r="L173" s="6"/>
-      <c r="M173" s="6"/>
-      <c r="N173" s="6"/>
-      <c r="O173" s="6"/>
-      <c r="P173" s="6"/>
-      <c r="Q173" s="6"/>
-      <c r="R173" s="6"/>
-      <c r="S173" s="6"/>
-      <c r="T173" s="6"/>
-      <c r="U173" s="6"/>
-      <c r="V173" s="6"/>
-      <c r="W173" s="6"/>
-      <c r="X173" s="6"/>
-      <c r="Y173" s="6"/>
-      <c r="Z173" s="6"/>
-      <c r="AA173" s="6"/>
-    </row>
-    <row r="174" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
-      <c r="L174" s="6"/>
-      <c r="M174" s="6"/>
-      <c r="N174" s="6"/>
-      <c r="O174" s="6"/>
-      <c r="P174" s="6"/>
-      <c r="Q174" s="6"/>
-      <c r="R174" s="6"/>
-      <c r="S174" s="6"/>
-      <c r="T174" s="6"/>
-      <c r="U174" s="6"/>
-      <c r="V174" s="6"/>
-      <c r="W174" s="6"/>
-      <c r="X174" s="6"/>
-      <c r="Y174" s="6"/>
-      <c r="Z174" s="6"/>
-      <c r="AA174" s="6"/>
-    </row>
-    <row r="175" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
-      <c r="M175" s="6"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="6"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="6"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="6"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="6"/>
+    <row r="169" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="4"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="1"/>
+      <c r="N169" s="1"/>
+      <c r="O169" s="1"/>
+      <c r="P169" s="1"/>
+      <c r="Q169" s="1"/>
+      <c r="R169" s="1"/>
+      <c r="S169" s="1"/>
+      <c r="T169" s="1"/>
+      <c r="U169" s="1"/>
+      <c r="V169" s="1"/>
+      <c r="W169" s="1"/>
+      <c r="X169" s="1"/>
+      <c r="Y169" s="1"/>
+      <c r="Z169" s="1"/>
+      <c r="AA169" s="1"/>
+    </row>
+    <row r="170" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="4"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+      <c r="L170" s="1"/>
+      <c r="M170" s="1"/>
+      <c r="N170" s="1"/>
+      <c r="O170" s="1"/>
+      <c r="P170" s="1"/>
+      <c r="Q170" s="1"/>
+      <c r="R170" s="1"/>
+      <c r="S170" s="1"/>
+      <c r="T170" s="1"/>
+      <c r="U170" s="1"/>
+      <c r="V170" s="1"/>
+      <c r="W170" s="1"/>
+      <c r="X170" s="1"/>
+      <c r="Y170" s="1"/>
+      <c r="Z170" s="1"/>
+      <c r="AA170" s="1"/>
+    </row>
+    <row r="171" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+      <c r="L171" s="1"/>
+      <c r="M171" s="1"/>
+      <c r="N171" s="1"/>
+      <c r="O171" s="1"/>
+      <c r="P171" s="1"/>
+      <c r="Q171" s="1"/>
+      <c r="R171" s="1"/>
+      <c r="S171" s="1"/>
+      <c r="T171" s="1"/>
+      <c r="U171" s="1"/>
+      <c r="V171" s="1"/>
+      <c r="W171" s="1"/>
+      <c r="X171" s="1"/>
+      <c r="Y171" s="1"/>
+      <c r="Z171" s="1"/>
+      <c r="AA171" s="1"/>
+    </row>
+    <row r="172" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="4"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="4"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+      <c r="L172" s="1"/>
+      <c r="M172" s="1"/>
+      <c r="N172" s="1"/>
+      <c r="O172" s="1"/>
+      <c r="P172" s="1"/>
+      <c r="Q172" s="1"/>
+      <c r="R172" s="1"/>
+      <c r="S172" s="1"/>
+      <c r="T172" s="1"/>
+      <c r="U172" s="1"/>
+      <c r="V172" s="1"/>
+      <c r="W172" s="1"/>
+      <c r="X172" s="1"/>
+      <c r="Y172" s="1"/>
+      <c r="Z172" s="1"/>
+      <c r="AA172" s="1"/>
+    </row>
+    <row r="173" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="4"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+      <c r="L173" s="1"/>
+      <c r="M173" s="1"/>
+      <c r="N173" s="1"/>
+      <c r="O173" s="1"/>
+      <c r="P173" s="1"/>
+      <c r="Q173" s="1"/>
+      <c r="R173" s="1"/>
+      <c r="S173" s="1"/>
+      <c r="T173" s="1"/>
+      <c r="U173" s="1"/>
+      <c r="V173" s="1"/>
+      <c r="W173" s="1"/>
+      <c r="X173" s="1"/>
+      <c r="Y173" s="1"/>
+      <c r="Z173" s="1"/>
+      <c r="AA173" s="1"/>
+    </row>
+    <row r="174" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="4"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="4"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+      <c r="L174" s="1"/>
+      <c r="M174" s="1"/>
+      <c r="N174" s="1"/>
+      <c r="O174" s="1"/>
+      <c r="P174" s="1"/>
+      <c r="Q174" s="1"/>
+      <c r="R174" s="1"/>
+      <c r="S174" s="1"/>
+      <c r="T174" s="1"/>
+      <c r="U174" s="1"/>
+      <c r="V174" s="1"/>
+      <c r="W174" s="1"/>
+      <c r="X174" s="1"/>
+      <c r="Y174" s="1"/>
+      <c r="Z174" s="1"/>
+      <c r="AA174" s="1"/>
+    </row>
+    <row r="175" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="4"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="4"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1"/>
+      <c r="M175" s="1"/>
+      <c r="N175" s="1"/>
+      <c r="O175" s="1"/>
+      <c r="P175" s="1"/>
+      <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+      <c r="S175" s="1"/>
+      <c r="T175" s="1"/>
+      <c r="U175" s="1"/>
+      <c r="V175" s="1"/>
+      <c r="W175" s="1"/>
+      <c r="X175" s="1"/>
+      <c r="Y175" s="1"/>
+      <c r="Z175" s="1"/>
+      <c r="AA175" s="1"/>
     </row>
     <row r="176" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6"/>
@@ -29343,56 +29472,227 @@
       <c r="Z942" s="6"/>
       <c r="AA942" s="6"/>
     </row>
+    <row r="943" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A943" s="6"/>
+      <c r="B943" s="6"/>
+      <c r="C943" s="6"/>
+      <c r="D943" s="6"/>
+      <c r="E943" s="6"/>
+      <c r="F943" s="6"/>
+      <c r="G943" s="6"/>
+      <c r="H943" s="6"/>
+      <c r="I943" s="6"/>
+      <c r="J943" s="6"/>
+      <c r="K943" s="6"/>
+      <c r="L943" s="6"/>
+      <c r="M943" s="6"/>
+      <c r="N943" s="6"/>
+      <c r="O943" s="6"/>
+      <c r="P943" s="6"/>
+      <c r="Q943" s="6"/>
+      <c r="R943" s="6"/>
+      <c r="S943" s="6"/>
+      <c r="T943" s="6"/>
+      <c r="U943" s="6"/>
+      <c r="V943" s="6"/>
+      <c r="W943" s="6"/>
+      <c r="X943" s="6"/>
+      <c r="Y943" s="6"/>
+      <c r="Z943" s="6"/>
+      <c r="AA943" s="6"/>
+    </row>
+    <row r="944" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A944" s="6"/>
+      <c r="B944" s="6"/>
+      <c r="C944" s="6"/>
+      <c r="D944" s="6"/>
+      <c r="E944" s="6"/>
+      <c r="F944" s="6"/>
+      <c r="G944" s="6"/>
+      <c r="H944" s="6"/>
+      <c r="I944" s="6"/>
+      <c r="J944" s="6"/>
+      <c r="K944" s="6"/>
+      <c r="L944" s="6"/>
+      <c r="M944" s="6"/>
+      <c r="N944" s="6"/>
+      <c r="O944" s="6"/>
+      <c r="P944" s="6"/>
+      <c r="Q944" s="6"/>
+      <c r="R944" s="6"/>
+      <c r="S944" s="6"/>
+      <c r="T944" s="6"/>
+      <c r="U944" s="6"/>
+      <c r="V944" s="6"/>
+      <c r="W944" s="6"/>
+      <c r="X944" s="6"/>
+      <c r="Y944" s="6"/>
+      <c r="Z944" s="6"/>
+      <c r="AA944" s="6"/>
+    </row>
+    <row r="945" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A945" s="6"/>
+      <c r="B945" s="6"/>
+      <c r="C945" s="6"/>
+      <c r="D945" s="6"/>
+      <c r="E945" s="6"/>
+      <c r="F945" s="6"/>
+      <c r="G945" s="6"/>
+      <c r="H945" s="6"/>
+      <c r="I945" s="6"/>
+      <c r="J945" s="6"/>
+      <c r="K945" s="6"/>
+      <c r="L945" s="6"/>
+      <c r="M945" s="6"/>
+      <c r="N945" s="6"/>
+      <c r="O945" s="6"/>
+      <c r="P945" s="6"/>
+      <c r="Q945" s="6"/>
+      <c r="R945" s="6"/>
+      <c r="S945" s="6"/>
+      <c r="T945" s="6"/>
+      <c r="U945" s="6"/>
+      <c r="V945" s="6"/>
+      <c r="W945" s="6"/>
+      <c r="X945" s="6"/>
+      <c r="Y945" s="6"/>
+      <c r="Z945" s="6"/>
+      <c r="AA945" s="6"/>
+    </row>
+    <row r="946" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A946" s="6"/>
+      <c r="B946" s="6"/>
+      <c r="C946" s="6"/>
+      <c r="D946" s="6"/>
+      <c r="E946" s="6"/>
+      <c r="F946" s="6"/>
+      <c r="G946" s="6"/>
+      <c r="H946" s="6"/>
+      <c r="I946" s="6"/>
+      <c r="J946" s="6"/>
+      <c r="K946" s="6"/>
+      <c r="L946" s="6"/>
+      <c r="M946" s="6"/>
+      <c r="N946" s="6"/>
+      <c r="O946" s="6"/>
+      <c r="P946" s="6"/>
+      <c r="Q946" s="6"/>
+      <c r="R946" s="6"/>
+      <c r="S946" s="6"/>
+      <c r="T946" s="6"/>
+      <c r="U946" s="6"/>
+      <c r="V946" s="6"/>
+      <c r="W946" s="6"/>
+      <c r="X946" s="6"/>
+      <c r="Y946" s="6"/>
+      <c r="Z946" s="6"/>
+      <c r="AA946" s="6"/>
+    </row>
+    <row r="947" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A947" s="6"/>
+      <c r="B947" s="6"/>
+      <c r="C947" s="6"/>
+      <c r="D947" s="6"/>
+      <c r="E947" s="6"/>
+      <c r="F947" s="6"/>
+      <c r="G947" s="6"/>
+      <c r="H947" s="6"/>
+      <c r="I947" s="6"/>
+      <c r="J947" s="6"/>
+      <c r="K947" s="6"/>
+      <c r="L947" s="6"/>
+      <c r="M947" s="6"/>
+      <c r="N947" s="6"/>
+      <c r="O947" s="6"/>
+      <c r="P947" s="6"/>
+      <c r="Q947" s="6"/>
+      <c r="R947" s="6"/>
+      <c r="S947" s="6"/>
+      <c r="T947" s="6"/>
+      <c r="U947" s="6"/>
+      <c r="V947" s="6"/>
+      <c r="W947" s="6"/>
+      <c r="X947" s="6"/>
+      <c r="Y947" s="6"/>
+      <c r="Z947" s="6"/>
+      <c r="AA947" s="6"/>
+    </row>
+    <row r="948" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A948" s="6"/>
+      <c r="B948" s="6"/>
+      <c r="C948" s="6"/>
+      <c r="D948" s="6"/>
+      <c r="E948" s="6"/>
+      <c r="F948" s="6"/>
+      <c r="G948" s="6"/>
+      <c r="H948" s="6"/>
+      <c r="I948" s="6"/>
+      <c r="J948" s="6"/>
+      <c r="K948" s="6"/>
+      <c r="L948" s="6"/>
+      <c r="M948" s="6"/>
+      <c r="N948" s="6"/>
+      <c r="O948" s="6"/>
+      <c r="P948" s="6"/>
+      <c r="Q948" s="6"/>
+      <c r="R948" s="6"/>
+      <c r="S948" s="6"/>
+      <c r="T948" s="6"/>
+      <c r="U948" s="6"/>
+      <c r="V948" s="6"/>
+      <c r="W948" s="6"/>
+      <c r="X948" s="6"/>
+      <c r="Y948" s="6"/>
+      <c r="Z948" s="6"/>
+      <c r="AA948" s="6"/>
+    </row>
+    <row r="949" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A949" s="6"/>
+      <c r="B949" s="6"/>
+      <c r="C949" s="6"/>
+      <c r="D949" s="6"/>
+      <c r="E949" s="6"/>
+      <c r="F949" s="6"/>
+      <c r="G949" s="6"/>
+      <c r="H949" s="6"/>
+      <c r="I949" s="6"/>
+      <c r="J949" s="6"/>
+      <c r="K949" s="6"/>
+      <c r="L949" s="6"/>
+      <c r="M949" s="6"/>
+      <c r="N949" s="6"/>
+      <c r="O949" s="6"/>
+      <c r="P949" s="6"/>
+      <c r="Q949" s="6"/>
+      <c r="R949" s="6"/>
+      <c r="S949" s="6"/>
+      <c r="T949" s="6"/>
+      <c r="U949" s="6"/>
+      <c r="V949" s="6"/>
+      <c r="W949" s="6"/>
+      <c r="X949" s="6"/>
+      <c r="Y949" s="6"/>
+      <c r="Z949" s="6"/>
+      <c r="AA949" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B29:C29"/>
+  <mergeCells count="83">
+    <mergeCell ref="A24:A27"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A22:C23"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G5:J7"/>
     <mergeCell ref="I2:J2"/>
@@ -29409,14 +29709,57 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E6:F7"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A22:C23"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -29431,7 +29774,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA948"/>
+  <dimension ref="A1:AA950"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -29448,134 +29791,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="40" t="s">
+      <c r="B2" s="118"/>
+      <c r="C2" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="45" t="s">
+      <c r="D2" s="111"/>
+      <c r="E2" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="39" t="s">
+      <c r="F2" s="115"/>
+      <c r="G2" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="95"/>
+      <c r="I2" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="39"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="47" t="s">
+      <c r="A3" s="117"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="50" t="s">
+      <c r="F3" s="116"/>
+      <c r="G3" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="50"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="98"/>
+      <c r="C4" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="61" t="s">
-        <v>106</v>
+      <c r="D4" s="94"/>
+      <c r="E4" s="105" t="s">
+        <v>101</v>
       </c>
-      <c r="F4" s="62"/>
-      <c r="G4" s="50" t="s">
+      <c r="F4" s="106"/>
+      <c r="G4" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="63" t="s">
+      <c r="A5" s="98"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="56" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="136" t="s">
-        <v>107</v>
+      <c r="D6" s="100"/>
+      <c r="E6" s="83" t="s">
+        <v>102</v>
       </c>
-      <c r="F6" s="66"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
     </row>
     <row r="7" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="101"/>
     </row>
     <row r="9" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
@@ -29596,14 +29939,14 @@
       <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58" t="s">
+      <c r="H9" s="102"/>
+      <c r="I9" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="102"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -29624,7 +29967,7 @@
     </row>
     <row r="10" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2">
         <v>8</v>
@@ -29641,14 +29984,14 @@
       <c r="F10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="51" t="s">
+      <c r="H10" s="104"/>
+      <c r="I10" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="52"/>
+      <c r="J10" s="96"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -29675,7 +30018,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>78</v>
@@ -29686,14 +30029,14 @@
       <c r="F11" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="59" t="s">
+      <c r="G11" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="60"/>
-      <c r="I11" s="51" t="s">
+      <c r="H11" s="104"/>
+      <c r="I11" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="52"/>
+      <c r="J11" s="96"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -29731,14 +30074,14 @@
       <c r="F12" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="G12" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="60"/>
-      <c r="I12" s="51" t="s">
+      <c r="H12" s="104"/>
+      <c r="I12" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="52"/>
+      <c r="J12" s="96"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -29769,10 +30112,10 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="122"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -29792,18 +30135,18 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="125"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="47"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -29823,18 +30166,18 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="126" t="s">
+      <c r="A15" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -29854,18 +30197,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="104" t="s">
-        <v>93</v>
+      <c r="A16" s="44" t="s">
+        <v>90</v>
       </c>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -29885,18 +30228,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -29916,18 +30259,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="240" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="104" t="s">
-        <v>109</v>
+      <c r="A18" s="44" t="s">
+        <v>104</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
@@ -29943,18 +30286,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="126" t="s">
+      <c r="A19" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -29974,18 +30317,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="104" t="s">
-        <v>94</v>
+      <c r="A20" s="44" t="s">
+        <v>91</v>
       </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -30005,18 +30348,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="105"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -30036,22 +30379,22 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="101" t="s">
+      <c r="A22" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="103" t="s">
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="106" t="s">
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -30071,12 +30414,12 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="102"/>
-      <c r="B23" s="102"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
       <c r="G23" s="21">
         <v>1</v>
       </c>
@@ -30107,22 +30450,22 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69" t="s">
+    <row r="24" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="145"/>
+      <c r="B24" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="70"/>
-      <c r="D24" s="71" t="s">
-        <v>91</v>
+      <c r="C24" s="126"/>
+      <c r="D24" s="80" t="s">
+        <v>108</v>
       </c>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
       <c r="G24" s="7"/>
       <c r="H24" s="18"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="1"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -30140,17 +30483,15 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="68"/>
-      <c r="B25" s="127" t="s">
-        <v>80</v>
+    <row r="25" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="87"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="80" t="s">
+        <v>109</v>
       </c>
-      <c r="C25" s="128"/>
-      <c r="D25" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="75"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
       <c r="G25" s="7"/>
       <c r="H25" s="18"/>
       <c r="I25" s="14"/>
@@ -30173,15 +30514,17 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="68"/>
-      <c r="B26" s="129"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="77" t="s">
-        <v>98</v>
+    <row r="26" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="87"/>
+      <c r="B26" s="125" t="s">
+        <v>80</v>
       </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="73"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
       <c r="G26" s="7"/>
       <c r="H26" s="18"/>
       <c r="I26" s="14"/>
@@ -30205,16 +30548,14 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="68"/>
-      <c r="B27" s="131" t="s">
-        <v>88</v>
+      <c r="A27" s="87"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="129" t="s">
+        <v>95</v>
       </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="74"/>
-      <c r="F27" s="75"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="77"/>
       <c r="G27" s="7"/>
       <c r="H27" s="18"/>
       <c r="I27" s="14"/>
@@ -30237,15 +30578,17 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="68"/>
-      <c r="B28" s="132"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="134" t="s">
-        <v>99</v>
+    <row r="28" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="87"/>
+      <c r="B28" s="131" t="s">
+        <v>87</v>
       </c>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="80" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="81"/>
+      <c r="F28" s="82"/>
       <c r="G28" s="7"/>
       <c r="H28" s="18"/>
       <c r="I28" s="14"/>
@@ -30268,17 +30611,15 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="68"/>
-      <c r="B29" s="114" t="s">
-        <v>77</v>
+    <row r="29" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="87"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="134"/>
+      <c r="D29" s="119" t="s">
+        <v>96</v>
       </c>
-      <c r="C29" s="115"/>
-      <c r="D29" s="116" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="117"/>
-      <c r="F29" s="118"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="121"/>
       <c r="G29" s="7"/>
       <c r="H29" s="18"/>
       <c r="I29" s="14"/>
@@ -30301,19 +30642,17 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="87" t="s">
-        <v>27</v>
+    <row r="30" spans="1:27" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="87"/>
+      <c r="B30" s="122" t="s">
+        <v>77</v>
       </c>
-      <c r="B30" s="84" t="s">
-        <v>38</v>
+      <c r="C30" s="123"/>
+      <c r="D30" s="124" t="s">
+        <v>89</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="71" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="121"/>
       <c r="G30" s="7"/>
       <c r="H30" s="18"/>
       <c r="I30" s="14"/>
@@ -30337,16 +30676,18 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="88"/>
-      <c r="B31" s="84" t="s">
-        <v>43</v>
+      <c r="A31" s="78" t="s">
+        <v>27</v>
       </c>
-      <c r="C31" s="85"/>
-      <c r="D31" s="86" t="s">
-        <v>59</v>
+      <c r="B31" s="73" t="s">
+        <v>38</v>
       </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82"/>
       <c r="G31" s="7"/>
       <c r="H31" s="18"/>
       <c r="I31" s="14"/>
@@ -30370,16 +30711,16 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="88"/>
-      <c r="B32" s="84" t="s">
-        <v>39</v>
+      <c r="A32" s="79"/>
+      <c r="B32" s="73" t="s">
+        <v>43</v>
       </c>
-      <c r="C32" s="85"/>
-      <c r="D32" s="86" t="s">
-        <v>95</v>
+      <c r="C32" s="74"/>
+      <c r="D32" s="75" t="s">
+        <v>59</v>
       </c>
-      <c r="E32" s="72"/>
-      <c r="F32" s="73"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77"/>
       <c r="G32" s="7"/>
       <c r="H32" s="18"/>
       <c r="I32" s="14"/>
@@ -30403,16 +30744,16 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="88"/>
-      <c r="B33" s="84" t="s">
-        <v>60</v>
+      <c r="A33" s="79"/>
+      <c r="B33" s="73" t="s">
+        <v>39</v>
       </c>
-      <c r="C33" s="85"/>
-      <c r="D33" s="86" t="s">
-        <v>89</v>
+      <c r="C33" s="74"/>
+      <c r="D33" s="75" t="s">
+        <v>92</v>
       </c>
-      <c r="E33" s="72"/>
-      <c r="F33" s="73"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="77"/>
       <c r="G33" s="7"/>
       <c r="H33" s="18"/>
       <c r="I33" s="14"/>
@@ -30435,17 +30776,21 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="83"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+    <row r="34" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="79"/>
+      <c r="B34" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="74"/>
+      <c r="D34" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="76"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -30465,18 +30810,14 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="79" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="80"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="80"/>
-      <c r="H35" s="81"/>
+      <c r="A35" s="72"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -30498,20 +30839,18 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
-        <v>6</v>
+      <c r="A36" s="68" t="s">
+        <v>12</v>
       </c>
-      <c r="B36" s="93" t="s">
-        <v>14</v>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="71" t="s">
+        <v>13</v>
       </c>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="92">
-        <v>100</v>
-      </c>
-      <c r="G36" s="90"/>
-      <c r="H36" s="91"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="70"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -30532,21 +30871,21 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
-      <c r="B37" s="100" t="s">
-        <v>57</v>
+      <c r="B37" s="50" t="s">
+        <v>14</v>
       </c>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="92">
-        <v>90</v>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="53">
+        <v>100</v>
       </c>
-      <c r="G37" s="90"/>
-      <c r="H37" s="91"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -30567,21 +30906,21 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B38" s="94" t="s">
-        <v>54</v>
+      <c r="B38" s="67" t="s">
+        <v>115</v>
       </c>
-      <c r="C38" s="95"/>
-      <c r="D38" s="95"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="97">
-        <v>80</v>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53">
+        <v>95</v>
       </c>
-      <c r="G38" s="98"/>
-      <c r="H38" s="99"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -30602,21 +30941,21 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
-      <c r="B39" s="94" t="s">
-        <v>55</v>
+      <c r="B39" s="67" t="s">
+        <v>57</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="96"/>
-      <c r="F39" s="97">
-        <v>70</v>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="53">
+        <v>90</v>
       </c>
-      <c r="G39" s="98"/>
-      <c r="H39" s="99"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="52"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -30637,21 +30976,21 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
-      <c r="B40" s="100" t="s">
-        <v>56</v>
+      <c r="B40" s="61" t="s">
+        <v>54</v>
       </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="92">
-        <v>60</v>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="64">
+        <v>80</v>
       </c>
-      <c r="G40" s="90"/>
-      <c r="H40" s="91"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="66"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -30672,21 +31011,21 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
-      <c r="B41" s="89" t="s">
-        <v>15</v>
+      <c r="B41" s="61" t="s">
+        <v>55</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="92">
-        <v>50</v>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="64">
+        <v>70</v>
       </c>
-      <c r="G41" s="90"/>
-      <c r="H41" s="91"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="66"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -30707,21 +31046,21 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
-      <c r="B42" s="93" t="s">
-        <v>16</v>
+      <c r="B42" s="67" t="s">
+        <v>56</v>
       </c>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="92">
-        <v>30</v>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="53">
+        <v>60</v>
       </c>
-      <c r="G42" s="90"/>
-      <c r="H42" s="91"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="52"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -30742,15 +31081,21 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
+    <row r="43" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>2</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53">
+        <v>50</v>
+      </c>
+      <c r="G43" s="51"/>
+      <c r="H43" s="52"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -30771,21 +31116,21 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="16" t="s">
-        <v>17</v>
+    <row r="44" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>1</v>
       </c>
-      <c r="E44" s="16" t="s">
-        <v>18</v>
+      <c r="B44" s="50" t="s">
+        <v>16</v>
       </c>
-      <c r="F44" s="16" t="s">
-        <v>19</v>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="53">
+        <v>30</v>
       </c>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="52"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -30806,25 +31151,15 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="109">
-        <v>1</v>
-      </c>
-      <c r="F45" s="109">
-        <v>0</v>
-      </c>
-      <c r="G45" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="H45" s="112" t="s">
-        <v>53</v>
-      </c>
+    <row r="45" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -30848,14 +31183,18 @@
     <row r="46" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="27" t="s">
-        <v>21</v>
+      <c r="C46" s="13"/>
+      <c r="D46" s="16" t="s">
+        <v>17</v>
       </c>
-      <c r="E46" s="110"/>
-      <c r="F46" s="110"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="113"/>
+      <c r="E46" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -30876,19 +31215,27 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
     </row>
-    <row r="47" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="108" t="s">
-        <v>36</v>
+    <row r="47" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="17" t="s">
+        <v>20</v>
       </c>
-      <c r="B47" s="108"/>
-      <c r="C47" s="108"/>
-      <c r="D47" s="108"/>
-      <c r="E47" s="108"/>
-      <c r="F47" s="108"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="108"/>
-      <c r="I47" s="108"/>
-      <c r="J47" s="108"/>
+      <c r="E47" s="54">
+        <v>1</v>
+      </c>
+      <c r="F47" s="54">
+        <v>0</v>
+      </c>
+      <c r="G47" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -30907,15 +31254,17 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
     </row>
-    <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="4"/>
+    <row r="48" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="59"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -30936,17 +31285,19 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
     </row>
-    <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+    <row r="49" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="49"/>
+      <c r="J49" s="49"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -34590,63 +34941,63 @@
       <c r="Z174" s="1"/>
       <c r="AA174" s="1"/>
     </row>
-    <row r="175" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
-      <c r="M175" s="6"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="6"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="6"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="6"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="6"/>
-    </row>
-    <row r="176" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
-      <c r="M176" s="6"/>
-      <c r="N176" s="6"/>
-      <c r="O176" s="6"/>
-      <c r="P176" s="6"/>
-      <c r="Q176" s="6"/>
-      <c r="R176" s="6"/>
-      <c r="S176" s="6"/>
-      <c r="T176" s="6"/>
-      <c r="U176" s="6"/>
-      <c r="V176" s="6"/>
-      <c r="W176" s="6"/>
-      <c r="X176" s="6"/>
-      <c r="Y176" s="6"/>
-      <c r="Z176" s="6"/>
-      <c r="AA176" s="6"/>
+    <row r="175" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="4"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="4"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1"/>
+      <c r="M175" s="1"/>
+      <c r="N175" s="1"/>
+      <c r="O175" s="1"/>
+      <c r="P175" s="1"/>
+      <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+      <c r="S175" s="1"/>
+      <c r="T175" s="1"/>
+      <c r="U175" s="1"/>
+      <c r="V175" s="1"/>
+      <c r="W175" s="1"/>
+      <c r="X175" s="1"/>
+      <c r="Y175" s="1"/>
+      <c r="Z175" s="1"/>
+      <c r="AA175" s="1"/>
+    </row>
+    <row r="176" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="4"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="4"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1"/>
+      <c r="M176" s="1"/>
+      <c r="N176" s="1"/>
+      <c r="O176" s="1"/>
+      <c r="P176" s="1"/>
+      <c r="Q176" s="1"/>
+      <c r="R176" s="1"/>
+      <c r="S176" s="1"/>
+      <c r="T176" s="1"/>
+      <c r="U176" s="1"/>
+      <c r="V176" s="1"/>
+      <c r="W176" s="1"/>
+      <c r="X176" s="1"/>
+      <c r="Y176" s="1"/>
+      <c r="Z176" s="1"/>
+      <c r="AA176" s="1"/>
     </row>
     <row r="177" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6"/>
@@ -57036,69 +57387,77 @@
       <c r="Z948" s="6"/>
       <c r="AA948" s="6"/>
     </row>
+    <row r="949" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A949" s="6"/>
+      <c r="B949" s="6"/>
+      <c r="C949" s="6"/>
+      <c r="D949" s="6"/>
+      <c r="E949" s="6"/>
+      <c r="F949" s="6"/>
+      <c r="G949" s="6"/>
+      <c r="H949" s="6"/>
+      <c r="I949" s="6"/>
+      <c r="J949" s="6"/>
+      <c r="K949" s="6"/>
+      <c r="L949" s="6"/>
+      <c r="M949" s="6"/>
+      <c r="N949" s="6"/>
+      <c r="O949" s="6"/>
+      <c r="P949" s="6"/>
+      <c r="Q949" s="6"/>
+      <c r="R949" s="6"/>
+      <c r="S949" s="6"/>
+      <c r="T949" s="6"/>
+      <c r="U949" s="6"/>
+      <c r="V949" s="6"/>
+      <c r="W949" s="6"/>
+      <c r="X949" s="6"/>
+      <c r="Y949" s="6"/>
+      <c r="Z949" s="6"/>
+      <c r="AA949" s="6"/>
+    </row>
+    <row r="950" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A950" s="6"/>
+      <c r="B950" s="6"/>
+      <c r="C950" s="6"/>
+      <c r="D950" s="6"/>
+      <c r="E950" s="6"/>
+      <c r="F950" s="6"/>
+      <c r="G950" s="6"/>
+      <c r="H950" s="6"/>
+      <c r="I950" s="6"/>
+      <c r="J950" s="6"/>
+      <c r="K950" s="6"/>
+      <c r="L950" s="6"/>
+      <c r="M950" s="6"/>
+      <c r="N950" s="6"/>
+      <c r="O950" s="6"/>
+      <c r="P950" s="6"/>
+      <c r="Q950" s="6"/>
+      <c r="R950" s="6"/>
+      <c r="S950" s="6"/>
+      <c r="T950" s="6"/>
+      <c r="U950" s="6"/>
+      <c r="V950" s="6"/>
+      <c r="W950" s="6"/>
+      <c r="X950" s="6"/>
+      <c r="Y950" s="6"/>
+      <c r="Z950" s="6"/>
+      <c r="AA950" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="F37:H37"/>
+  <mergeCells count="85">
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="F38:H38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:C23"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:J9"/>
@@ -57111,15 +57470,68 @@
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="C6:D7"/>
     <mergeCell ref="E6:F7"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:C23"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="A49:J49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>

--- a/ds/planejamento/1semestre/planos/Planos_de_Ensino_LER.xlsx
+++ b/ds/planejamento/1semestre/planos/Planos_de_Ensino_LER.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\senai2026\ds\planejamento\1semestre\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESENVOLVIMENTO\Desktop\senai2026\ds\planejamento\1semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0364BB-3448-492A-8A0A-BD10C356DBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E690821E-7CD1-41FA-9214-447431A8CFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano de Ensino1" sheetId="2" r:id="rId1"/>
     <sheet name="Plano de Ensino2" sheetId="4" r:id="rId2"/>
+    <sheet name="Trabalho em Grupo" sheetId="5" r:id="rId3"/>
+    <sheet name="Atividades Individuais" sheetId="6" r:id="rId4"/>
+    <sheet name="Trabalho em Grupo2" sheetId="7" r:id="rId5"/>
+    <sheet name="Sharktank" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="h9gkGl1sfnRHyr05LFfZmsKJ7cUyj85gDjaHNauDRX4="/>
     </ext>
@@ -35,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="152">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -623,6 +630,579 @@
 3. Demonstrar inteligência emocional	
 4 Demonstrar autonomia</t>
   </si>
+  <si>
+    <t>Atividades</t>
+  </si>
+  <si>
+    <t>Objetivo da aula</t>
+  </si>
+  <si>
+    <t>Em seu caderno, ilustre os requisitos funcionais a seguir através de DCUs, um para cada requisito.</t>
+  </si>
+  <si>
+    <t>1 - Sistema de controle de estoque de loja de roupas</t>
+  </si>
+  <si>
+    <r>
+      <t>[RF001] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tela de login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, contendo os campos email e senha e direcionando os </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>usuários</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Funcionários comuns e Gerência) para suas respectivas telas principais, caso suas credenciais sejam válidas, senão informa erro de login.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[RF002] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dashboard do estoque</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, tela com um relatório de movimentações no estoque em forma de tabela e gráfico comparando os investimentos (Compras de produtos) e as vendas efetivas, acessada somente pelo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>gerente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> da loja.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[RF003] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tela de cadastro de mercadorias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, contendo os campos básicos como id (identificação para evitar produtos duplicados, gerada automaticamente pelo sistema), nome, descrição, preço e quantidade, todos os campos são obrigatórios, possui um campo de busca por nome para verificar se a mercadoria já não está cadastrada, acessada pelo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>gerente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> da loja.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[RF004] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tela de registro de Entradas (Compras)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, contendo os dados de aquisição/compra de mercadorias como quantidade, custo unitário e despesas gerais, cada compra registrada altera a quantidade de produtos no cadastro acrescentando a quantidade adquirida, acessada pelos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>compradores</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> da loja.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[RF005] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tela de registro de Saídas (Vendas)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, contendo os dados do pedido de mercadorias como quantidade, preço unitário, subtotais, despesas de frete, mais impostos, valor total da venda. Cada venda registrada altera a quantidade de produtos no cadastro diminuindo a quantidade, acessada pelos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>vendedores</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> da loja.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[RF006] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tela de cadastro de novo funcionário</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, acessada somente pelo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>gerente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> da loja, onde ele preenche os dados no novo funcionário como nome, cargo, e-mail e senha provisória para que ele troque no primeiro acesso.</t>
+    </r>
+  </si>
+  <si>
+    <t>Documentar requisitos funcionais ilustrando através da UML de Diagramas de Casos de Uso</t>
+  </si>
+  <si>
+    <t>Documentar requisitos</t>
+  </si>
+  <si>
+    <t>Agora que já conhecemos ferramentas de ilustração para documentar os requisitos:</t>
+  </si>
+  <si>
+    <t>- 1 Ilustre cada requisito funcional com diagrama de caso de uso.</t>
+  </si>
+  <si>
+    <t>- 2 Crie um documento no Word formatado no formato ABNT contendo os seguintes capítulos:</t>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Descrição das regras de negócio numeradas em [RN001] até [RN00...]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Descrição dos requisitos funcionais ilustrados com DCU (Diagramas de casos de Uso), numerados em [RF001] até [RF00...]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Descrição dos requisitos não funcionais numerados em [NF001] até [NF00...]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wireframe das telas na versão de aplicativo móvel para celular e para site da internet.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Orçamento em forma de tabela contendo o tempo gasto para o desenvolvimento e os profissionais (programadores envolvidos no projeto)</t>
+    </r>
+  </si>
+  <si>
+    <t>Além de seguir a métrica padrão ABNT com Resumo, Introdução, Conclusão ou Resultados e Bibliografia</t>
+  </si>
+  <si>
+    <t>Trabalho em grupo</t>
+  </si>
+  <si>
+    <t>Contextualização</t>
+  </si>
+  <si>
+    <t>O Shark Tank Brasil é um reality show de empreendedorismo, exibido pelo Sony Channel, onde empreendedores apresentam suas empresas e planos de negócios a investidores renomados (os "tubarões"), buscando aporte financeiro em troca de participação societária. É a versão brasileira do formato internacional Dragons' Den</t>
+  </si>
+  <si>
+    <t>Desafio</t>
+  </si>
+  <si>
+    <t>Baseado neste programa de televisão monte um grupo empreendedor que deve resolver um problema desta escola.</t>
+  </si>
+  <si>
+    <t>Identifique um problema rotineiro que pode ser resolvido através da tecnologia e inovação, podendo ser com ou sem um programa de computador, porém lembre-se que neste curso estamos sendo formados, programadores de todas as stacks,  então soluções mais plausíveis geralmente terão o uso de programação.</t>
+  </si>
+  <si>
+    <t>Teremos tempo para:</t>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Identificar os problemas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elencar as regras de negócio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elencar requisitos funcionais</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elencar requisitos não funcionais</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Representar através de Wireframes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Desenvolver um protótipo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elaborar uma apresentação semelhante a do programa de televisão Shark Tank e convencer uma banca de professores, coordenadores e ou pais de aluno sobre o problema e a melhor solução</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -632,7 +1212,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -874,8 +1454,62 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Symbol"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F2328"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -900,8 +1534,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1319,11 +1959,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1418,16 +2074,67 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1457,10 +2164,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1468,23 +2172,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1507,6 +2195,25 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1549,6 +2256,18 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1558,14 +2277,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1576,8 +2292,38 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1587,9 +2333,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1653,6 +2396,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1671,23 +2426,11 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1695,50 +2438,15 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1837,6 +2545,55 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>667896</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>106002</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319C4363-F591-4059-93E4-AE4CD91EED37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8211696" cy="8792802"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2047,145 +2804,145 @@
     <col min="1" max="1" width="7.125" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="22.625" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="9.25" customWidth="1"/>
+    <col min="8" max="8" width="6.75" customWidth="1"/>
     <col min="9" max="9" width="9.375" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
+    <col min="10" max="17" width="8" customWidth="1"/>
     <col min="18" max="27" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="110" t="s">
+      <c r="B2" s="147"/>
+      <c r="C2" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="111"/>
-      <c r="E2" s="114" t="s">
+      <c r="D2" s="140"/>
+      <c r="E2" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="115"/>
-      <c r="G2" s="95" t="s">
+      <c r="F2" s="144"/>
+      <c r="G2" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95" t="s">
+      <c r="H2" s="125"/>
+      <c r="I2" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="95"/>
+      <c r="J2" s="125"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="116" t="s">
+      <c r="A3" s="146"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="145" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="116"/>
-      <c r="G3" s="93" t="s">
+      <c r="F3" s="145"/>
+      <c r="G3" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="93"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="94" t="s">
+      <c r="B4" s="127"/>
+      <c r="C4" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="105" t="s">
+      <c r="D4" s="124"/>
+      <c r="E4" s="134" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="106"/>
-      <c r="G4" s="93" t="s">
+      <c r="F4" s="135"/>
+      <c r="G4" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="98"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="107" t="s">
+      <c r="A5" s="127"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="108"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="100" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="100"/>
-      <c r="E6" s="83" t="s">
+      <c r="D6" s="129"/>
+      <c r="E6" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="84"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="98"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="101"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
     </row>
     <row r="9" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
@@ -2206,14 +2963,14 @@
       <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="102" t="s">
+      <c r="G9" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102" t="s">
+      <c r="H9" s="131"/>
+      <c r="I9" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="102"/>
+      <c r="J9" s="131"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2232,7 +2989,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="1:27" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="28" t="s">
         <v>46</v>
       </c>
@@ -2248,17 +3005,17 @@
       <c r="E10" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="138" t="s">
+      <c r="F10" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="103" t="s">
+      <c r="G10" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="104"/>
-      <c r="I10" s="103" t="s">
+      <c r="H10" s="133"/>
+      <c r="I10" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="J10" s="104"/>
+      <c r="J10" s="133"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2277,7 +3034,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" ht="165.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>47</v>
       </c>
@@ -2293,15 +3050,15 @@
       <c r="E11" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="139"/>
-      <c r="G11" s="103" t="s">
+      <c r="F11" s="119"/>
+      <c r="G11" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="104"/>
-      <c r="I11" s="38" t="s">
+      <c r="H11" s="133"/>
+      <c r="I11" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="96"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -2320,7 +3077,7 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>99</v>
       </c>
@@ -2336,15 +3093,15 @@
       <c r="E12" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="140"/>
-      <c r="G12" s="38" t="s">
+      <c r="F12" s="120"/>
+      <c r="G12" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="39"/>
-      <c r="I12" s="38" t="s">
+      <c r="H12" s="122"/>
+      <c r="I12" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="39"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2367,7 +3124,7 @@
       <c r="A13" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="163">
         <f>SUM(B7:B12)</f>
         <v>40</v>
       </c>
@@ -2375,10 +3132,10 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="60"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2398,18 +3155,18 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="64"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2429,18 +3186,18 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2460,18 +3217,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2491,18 +3248,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2522,18 +3279,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="233.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
@@ -2549,18 +3306,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2580,18 +3337,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2611,18 +3368,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="91" t="s">
+      <c r="A21" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="91"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2642,22 +3399,22 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="88" t="s">
+      <c r="A22" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="90" t="s">
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="56" t="s">
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2677,12 +3434,12 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="89"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
+      <c r="A23" s="109"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="21">
         <v>1</v>
       </c>
@@ -2714,22 +3471,22 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="125" t="s">
+      <c r="B24" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="126"/>
-      <c r="D24" s="80" t="s">
+      <c r="C24" s="115"/>
+      <c r="D24" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="77"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
       <c r="G24" s="7"/>
       <c r="H24" s="18"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="135"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
       <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2749,14 +3506,14 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="137"/>
-      <c r="B25" s="133"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="80" t="s">
+      <c r="A25" s="149"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="94"/>
       <c r="G25" s="7"/>
       <c r="H25" s="18"/>
       <c r="I25" s="19"/>
@@ -2780,16 +3537,16 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="137"/>
-      <c r="B26" s="125" t="s">
+      <c r="A26" s="149"/>
+      <c r="B26" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="126"/>
-      <c r="D26" s="80" t="s">
+      <c r="C26" s="115"/>
+      <c r="D26" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="94"/>
       <c r="G26" s="7"/>
       <c r="H26" s="18"/>
       <c r="I26" s="19"/>
@@ -2813,14 +3570,14 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="146"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="129" t="s">
+      <c r="A27" s="150"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="107" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="130"/>
-      <c r="F27" s="77"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="94"/>
       <c r="G27" s="7"/>
       <c r="H27" s="18"/>
       <c r="I27" s="14"/>
@@ -2844,18 +3601,18 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="74"/>
-      <c r="D28" s="80" t="s">
+      <c r="C28" s="91"/>
+      <c r="D28" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="99"/>
       <c r="G28" s="7"/>
       <c r="H28" s="18"/>
       <c r="I28" s="14"/>
@@ -2879,16 +3636,16 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="78"/>
-      <c r="B29" s="141" t="s">
+      <c r="A29" s="95"/>
+      <c r="B29" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="142"/>
-      <c r="D29" s="75" t="s">
+      <c r="C29" s="101"/>
+      <c r="D29" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="94"/>
       <c r="G29" s="7"/>
       <c r="H29" s="18"/>
       <c r="I29" s="14"/>
@@ -2912,14 +3669,14 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="79"/>
-      <c r="B30" s="143"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="75" t="s">
+      <c r="A30" s="96"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="94"/>
       <c r="G30" s="7"/>
       <c r="H30" s="18"/>
       <c r="I30" s="14"/>
@@ -2943,16 +3700,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="79"/>
-      <c r="B31" s="73" t="s">
+      <c r="A31" s="96"/>
+      <c r="B31" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="74"/>
-      <c r="D31" s="75" t="s">
+      <c r="C31" s="91"/>
+      <c r="D31" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="94"/>
       <c r="G31" s="7"/>
       <c r="H31" s="18"/>
       <c r="I31" s="14"/>
@@ -2976,16 +3733,16 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="79"/>
-      <c r="B32" s="141" t="s">
+      <c r="A32" s="96"/>
+      <c r="B32" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="142"/>
-      <c r="D32" s="75" t="s">
+      <c r="C32" s="101"/>
+      <c r="D32" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="94"/>
       <c r="G32" s="7"/>
       <c r="H32" s="18"/>
       <c r="I32" s="14"/>
@@ -3009,14 +3766,14 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="79"/>
-      <c r="B33" s="143"/>
-      <c r="C33" s="128"/>
-      <c r="D33" s="75" t="s">
+      <c r="A33" s="96"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="92" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="77"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="94"/>
       <c r="G33" s="7"/>
       <c r="H33" s="18"/>
       <c r="I33" s="14"/>
@@ -3040,14 +3797,14 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="72"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="89"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -3069,18 +3826,18 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="71" t="s">
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="69"/>
-      <c r="H35" s="70"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="87"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -3105,17 +3862,17 @@
       <c r="A36" s="8">
         <v>8</v>
       </c>
-      <c r="B36" s="50" t="s">
+      <c r="B36" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="53">
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="69">
         <v>100</v>
       </c>
-      <c r="G36" s="51"/>
-      <c r="H36" s="52"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="68"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -3140,17 +3897,17 @@
       <c r="A37" s="8">
         <v>7</v>
       </c>
-      <c r="B37" s="61" t="s">
+      <c r="B37" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="62"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="64">
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="74">
         <v>95</v>
       </c>
-      <c r="G37" s="65"/>
-      <c r="H37" s="66"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="76"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -3175,17 +3932,17 @@
       <c r="A38" s="8">
         <v>6</v>
       </c>
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="64">
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="74">
         <v>90</v>
       </c>
-      <c r="G38" s="65"/>
-      <c r="H38" s="66"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="76"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -3210,17 +3967,17 @@
       <c r="A39" s="8">
         <v>5</v>
       </c>
-      <c r="B39" s="61" t="s">
+      <c r="B39" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="64">
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="74">
         <v>80</v>
       </c>
-      <c r="G39" s="65"/>
-      <c r="H39" s="66"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="76"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -3245,17 +4002,17 @@
       <c r="A40" s="8">
         <v>4</v>
       </c>
-      <c r="B40" s="61" t="s">
+      <c r="B40" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="64">
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="74">
         <v>70</v>
       </c>
-      <c r="G40" s="65"/>
-      <c r="H40" s="66"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="76"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -3280,17 +4037,17 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="53">
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="69">
         <v>60</v>
       </c>
-      <c r="G41" s="51"/>
-      <c r="H41" s="52"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="68"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -3315,17 +4072,17 @@
       <c r="A42" s="8">
         <v>2</v>
       </c>
-      <c r="B42" s="60" t="s">
+      <c r="B42" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="53">
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="69">
         <v>50</v>
       </c>
-      <c r="G42" s="51"/>
-      <c r="H42" s="52"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="68"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3350,17 +4107,17 @@
       <c r="A43" s="8">
         <v>1</v>
       </c>
-      <c r="B43" s="50" t="s">
+      <c r="B43" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="53">
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="69">
         <v>30</v>
       </c>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="68"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3452,16 +4209,16 @@
       <c r="D46" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="54">
+      <c r="E46" s="79">
         <v>1</v>
       </c>
-      <c r="F46" s="54">
+      <c r="F46" s="79">
         <v>0</v>
       </c>
-      <c r="G46" s="88" t="s">
+      <c r="G46" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="58" t="s">
+      <c r="H46" s="83" t="s">
         <v>53</v>
       </c>
       <c r="I46" s="1"/>
@@ -3491,10 +4248,10 @@
       <c r="D47" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="144"/>
-      <c r="H47" s="59"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="84"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3516,18 +4273,18 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="78"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -29722,7 +30479,9 @@
     <mergeCell ref="B26:C27"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="F10:F12"/>
-    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="A34:H34"/>
@@ -29733,11 +30492,7 @@
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D33:F33"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="B29:C30"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A16:J16"/>
     <mergeCell ref="A48:J48"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="F43:H43"/>
@@ -29752,7 +30507,9 @@
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="F40:H40"/>
     <mergeCell ref="B41:E41"/>
-    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="I13:J13"/>
@@ -29762,9 +30519,16 @@
     <mergeCell ref="A17:J17"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I11:J11" location="'Trabalho em Grupo'!A1" display="Trabalho em grupo utilizando algumas das técnicas expostas, a fim de sugerir sistemas de informação para o tema pesquisado nas aulas anteriores. Atividades individuais. Lista de exercícios." xr:uid="{41553A2C-5513-46CA-A5C3-D0D4E5FEA006}"/>
+    <hyperlink ref="I12:J12" location="'Trabalho em Grupo'!A1" display="Trabaho em grupo, simulação de entrevista, Documentação dos requisitos levantados, apresentação dos resultados em forma de seminário." xr:uid="{C3FD198D-9773-4BEB-ABFE-77A89C205B56}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="13" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -29778,147 +30542,148 @@
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="22.625" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="9.375" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="7.75" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="6" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="8" width="7.375" customWidth="1"/>
+    <col min="9" max="9" width="6.5" customWidth="1"/>
+    <col min="10" max="10" width="6.75" customWidth="1"/>
     <col min="11" max="17" width="8" customWidth="1"/>
     <col min="18" max="27" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="110" t="s">
+      <c r="B2" s="147"/>
+      <c r="C2" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="111"/>
-      <c r="E2" s="114" t="s">
+      <c r="D2" s="140"/>
+      <c r="E2" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="115"/>
-      <c r="G2" s="95" t="s">
+      <c r="F2" s="144"/>
+      <c r="G2" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95" t="s">
+      <c r="H2" s="125"/>
+      <c r="I2" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="95"/>
+      <c r="J2" s="125"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="116" t="s">
+      <c r="A3" s="146"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="145" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="116"/>
-      <c r="G3" s="93" t="s">
+      <c r="F3" s="145"/>
+      <c r="G3" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="93"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="94" t="s">
+      <c r="B4" s="127"/>
+      <c r="C4" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="105" t="s">
+      <c r="D4" s="124"/>
+      <c r="E4" s="134" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="106"/>
-      <c r="G4" s="93" t="s">
+      <c r="F4" s="135"/>
+      <c r="G4" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="98"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="107" t="s">
+      <c r="A5" s="127"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="108"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="100" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="100"/>
-      <c r="E6" s="83" t="s">
+      <c r="D6" s="129"/>
+      <c r="E6" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="84"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="98"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="101"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
     </row>
     <row r="9" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
@@ -29939,14 +30704,14 @@
       <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="102" t="s">
+      <c r="G9" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102" t="s">
+      <c r="H9" s="131"/>
+      <c r="I9" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="102"/>
+      <c r="J9" s="131"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -29965,7 +30730,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="248.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
         <v>103</v>
       </c>
@@ -29984,14 +30749,14 @@
       <c r="F10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="103" t="s">
+      <c r="G10" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="104"/>
-      <c r="I10" s="38" t="s">
+      <c r="H10" s="133"/>
+      <c r="I10" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="96"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -30010,7 +30775,7 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="165.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="248.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>49</v>
       </c>
@@ -30026,17 +30791,17 @@
       <c r="E11" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="103" t="s">
+      <c r="G11" s="132" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="104"/>
-      <c r="I11" s="38" t="s">
+      <c r="H11" s="133"/>
+      <c r="I11" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="96"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -30055,7 +30820,7 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="248.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28" t="s">
         <v>50</v>
       </c>
@@ -30071,17 +30836,17 @@
       <c r="E12" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="103" t="s">
+      <c r="G12" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="104"/>
-      <c r="I12" s="38" t="s">
+      <c r="H12" s="133"/>
+      <c r="I12" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="96"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -30104,7 +30869,7 @@
       <c r="A13" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="163">
         <f>SUM(B7:B12)</f>
         <v>40</v>
       </c>
@@ -30112,10 +30877,10 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="60"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -30135,18 +30900,18 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="64"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -30166,18 +30931,18 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -30197,18 +30962,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -30228,18 +30993,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -30259,18 +31024,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="240" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
@@ -30286,18 +31051,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -30317,18 +31082,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -30348,18 +31113,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="91" t="s">
+      <c r="A21" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="91"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -30379,22 +31144,22 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="88" t="s">
+      <c r="A22" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="90" t="s">
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="56" t="s">
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -30414,12 +31179,12 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="89"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
+      <c r="A23" s="109"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="21">
         <v>1</v>
       </c>
@@ -30451,16 +31216,16 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="145"/>
-      <c r="B24" s="125" t="s">
+      <c r="A24" s="38"/>
+      <c r="B24" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="126"/>
-      <c r="D24" s="80" t="s">
+      <c r="C24" s="115"/>
+      <c r="D24" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="77"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
       <c r="G24" s="7"/>
       <c r="H24" s="18"/>
       <c r="I24" s="22"/>
@@ -30484,14 +31249,14 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="87"/>
-      <c r="B25" s="133"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="80" t="s">
+      <c r="A25" s="158"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="94"/>
       <c r="G25" s="7"/>
       <c r="H25" s="18"/>
       <c r="I25" s="14"/>
@@ -30515,16 +31280,16 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="87"/>
-      <c r="B26" s="125" t="s">
+      <c r="A26" s="158"/>
+      <c r="B26" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="126"/>
-      <c r="D26" s="80" t="s">
+      <c r="C26" s="115"/>
+      <c r="D26" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="81"/>
-      <c r="F26" s="82"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="7"/>
       <c r="H26" s="18"/>
       <c r="I26" s="14"/>
@@ -30548,14 +31313,14 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="87"/>
-      <c r="B27" s="127"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129" t="s">
+      <c r="A27" s="158"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="130"/>
-      <c r="F27" s="77"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="94"/>
       <c r="G27" s="7"/>
       <c r="H27" s="18"/>
       <c r="I27" s="14"/>
@@ -30579,16 +31344,16 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="87"/>
-      <c r="B28" s="131" t="s">
+      <c r="A28" s="158"/>
+      <c r="B28" s="160" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="132"/>
-      <c r="D28" s="80" t="s">
+      <c r="C28" s="161"/>
+      <c r="D28" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="99"/>
       <c r="G28" s="7"/>
       <c r="H28" s="18"/>
       <c r="I28" s="14"/>
@@ -30612,14 +31377,14 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="87"/>
-      <c r="B29" s="133"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="119" t="s">
+      <c r="A29" s="158"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="152" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="120"/>
-      <c r="F29" s="121"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="154"/>
       <c r="G29" s="7"/>
       <c r="H29" s="18"/>
       <c r="I29" s="14"/>
@@ -30643,16 +31408,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="87"/>
-      <c r="B30" s="122" t="s">
+      <c r="A30" s="158"/>
+      <c r="B30" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="124" t="s">
+      <c r="C30" s="156"/>
+      <c r="D30" s="157" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="120"/>
-      <c r="F30" s="121"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="154"/>
       <c r="G30" s="7"/>
       <c r="H30" s="18"/>
       <c r="I30" s="14"/>
@@ -30676,18 +31441,18 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="74"/>
-      <c r="D31" s="80" t="s">
+      <c r="C31" s="91"/>
+      <c r="D31" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="99"/>
       <c r="G31" s="7"/>
       <c r="H31" s="18"/>
       <c r="I31" s="14"/>
@@ -30711,16 +31476,16 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="79"/>
-      <c r="B32" s="73" t="s">
+      <c r="A32" s="96"/>
+      <c r="B32" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="74"/>
-      <c r="D32" s="75" t="s">
+      <c r="C32" s="91"/>
+      <c r="D32" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="94"/>
       <c r="G32" s="7"/>
       <c r="H32" s="18"/>
       <c r="I32" s="14"/>
@@ -30744,16 +31509,16 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="79"/>
-      <c r="B33" s="73" t="s">
+      <c r="A33" s="96"/>
+      <c r="B33" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="74"/>
-      <c r="D33" s="75" t="s">
+      <c r="C33" s="91"/>
+      <c r="D33" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="77"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="94"/>
       <c r="G33" s="7"/>
       <c r="H33" s="18"/>
       <c r="I33" s="14"/>
@@ -30777,16 +31542,16 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="79"/>
-      <c r="B34" s="73" t="s">
+      <c r="A34" s="96"/>
+      <c r="B34" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="75" t="s">
+      <c r="C34" s="91"/>
+      <c r="D34" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="E34" s="76"/>
-      <c r="F34" s="77"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94"/>
       <c r="G34" s="7"/>
       <c r="H34" s="18"/>
       <c r="I34" s="14"/>
@@ -30810,14 +31575,14 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
+      <c r="A35" s="89"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="89"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -30839,18 +31604,18 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="68" t="s">
+      <c r="A36" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="71" t="s">
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="69"/>
-      <c r="H36" s="70"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="87"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -30875,17 +31640,17 @@
       <c r="A37" s="8">
         <v>8</v>
       </c>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="53">
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="69">
         <v>100</v>
       </c>
-      <c r="G37" s="51"/>
-      <c r="H37" s="52"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="68"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -30910,17 +31675,17 @@
       <c r="A38" s="8">
         <v>7</v>
       </c>
-      <c r="B38" s="67" t="s">
+      <c r="B38" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53">
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="69">
         <v>95</v>
       </c>
-      <c r="G38" s="51"/>
-      <c r="H38" s="52"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="68"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -30945,17 +31710,17 @@
       <c r="A39" s="8">
         <v>6</v>
       </c>
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="53">
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="69">
         <v>90</v>
       </c>
-      <c r="G39" s="51"/>
-      <c r="H39" s="52"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="68"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -30980,17 +31745,17 @@
       <c r="A40" s="8">
         <v>5</v>
       </c>
-      <c r="B40" s="61" t="s">
+      <c r="B40" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="64">
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="74">
         <v>80</v>
       </c>
-      <c r="G40" s="65"/>
-      <c r="H40" s="66"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="76"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -31015,17 +31780,17 @@
       <c r="A41" s="8">
         <v>4</v>
       </c>
-      <c r="B41" s="61" t="s">
+      <c r="B41" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="62"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="64">
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="74">
         <v>70</v>
       </c>
-      <c r="G41" s="65"/>
-      <c r="H41" s="66"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="76"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -31050,17 +31815,17 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="67" t="s">
+      <c r="B42" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="53">
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="69">
         <v>60</v>
       </c>
-      <c r="G42" s="51"/>
-      <c r="H42" s="52"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="68"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -31085,17 +31850,17 @@
       <c r="A43" s="8">
         <v>2</v>
       </c>
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="53">
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="69">
         <v>50</v>
       </c>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="68"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -31120,17 +31885,17 @@
       <c r="A44" s="8">
         <v>1</v>
       </c>
-      <c r="B44" s="50" t="s">
+      <c r="B44" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="53">
+      <c r="C44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="69">
         <v>30</v>
       </c>
-      <c r="G44" s="51"/>
-      <c r="H44" s="52"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="68"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -31222,16 +31987,16 @@
       <c r="D47" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="54">
+      <c r="E47" s="79">
         <v>1</v>
       </c>
-      <c r="F47" s="54">
+      <c r="F47" s="79">
         <v>0</v>
       </c>
-      <c r="G47" s="56" t="s">
+      <c r="G47" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="H47" s="58" t="s">
+      <c r="H47" s="83" t="s">
         <v>53</v>
       </c>
       <c r="I47" s="1"/>
@@ -31261,10 +32026,10 @@
       <c r="D48" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="59"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="151"/>
+      <c r="H48" s="84"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -31286,18 +32051,18 @@
       <c r="AA48" s="1"/>
     </row>
     <row r="49" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="49" t="s">
+      <c r="A49" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="49"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="78"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="78"/>
+      <c r="H49" s="78"/>
+      <c r="I49" s="78"/>
+      <c r="J49" s="78"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -57498,13 +58263,18 @@
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="F37:H37"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="F37:H37"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="B33:C33"/>
@@ -57514,28 +58284,261 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="F40:H40"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="F42:H42"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A49:J49"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="F44:H44"/>
     <mergeCell ref="E47:E48"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="H47:H48"/>
-    <mergeCell ref="A49:J49"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I10:J10" location="'Trabalho em Grupo2'!A1" display="Trabaho em grupo, simulação de entrevista, Documentação dos requisitos levantados, apresentação dos resultados em forma de seminário." xr:uid="{B5FFB77A-B86D-4A73-B5E5-6229FBE649AD}"/>
+    <hyperlink ref="I11:J11" location="Sharktank!A1" display="Trabalho em grupo, exposição dialogada, pesquisa utilizando a internet." xr:uid="{4C3A65B0-18A6-4304-B10D-C9F4E02938B8}"/>
+    <hyperlink ref="I12:J12" location="Sharktank!A1" display="Projeto, Empresa modelo, proposta de solução de problema. Apresentação de resultados através de eminário." xr:uid="{C86CED2D-7059-4C25-9620-05A33A8E3772}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="13" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDC3C06-BBF1-486D-8577-32EA81583851}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49400B26-014E-429D-A948-1EEC034A2A6E}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultColWidth="106.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="41" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="69" x14ac:dyDescent="0.2">
+      <c r="A6" s="40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C3CEA7-885C-47C5-86D2-8F12406BFA00}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="138.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A2" s="43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="44" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A9" s="47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="47" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2EC06D-0056-4CB2-ACB1-A3FBB690F045}">
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="100" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="69" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="54" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A9" s="54" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="54" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="54" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="54" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="54" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>